--- a/output_phyto/phyto_Intermediate_zhang_2020.xlsx
+++ b/output_phyto/phyto_Intermediate_zhang_2020.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="409">
   <si>
     <t>NA</t>
   </si>
@@ -1454,124 +1454,421 @@
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.gca.2020.05.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_p1.0.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harper and Giulivi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dong et al., 2016. Tuned high-resolution Tex86 record to EPICA Dome C CO2 record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mk37_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">published Uk37 temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA; PO4 is not used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caculated using the empirical relationship between cell radius (r) and coccolith length (L) r=0.44*L+0.28 (Henderiks and Pagani, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The calculation of d13C_CO2aq follows Zhang et al. (2013). Subtracted 0.5‰ from the d13C_CaCO3 value reported in the supplementary table of Zhang et al. (2020) to get back to actual measured foraminifera d13C, since the reported value in the table includes the vital effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_35</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_22</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1016/j.gca.2020.05.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_zhang_2020.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harper and Giulivi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dong et al., 2016. Tuned high-resolution Tex86 record to EPICA Dome C CO2 record.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mk37_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No phosphate needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caculated using the empirical relationship between cell radius (r) and coccolith length (L) r=0.44*L+0.28 (Henderiks and Pagani, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The calculation of d13C_CO2aq follows Zhang et al. (2013). Subtracted 0.5‰ from the d13C_CaCO3 value reported in the supplementary table of Zhang et al. (2020) to get back to actual measured foraminifera d13C, since the reported value in the table includes the vital effect.</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The calculation of d13C_CO2aq  follows Zhang et al. (2013). SP: Coccolith size is not measured, but interpolated from two samples of Bolton et al., 2016 ~1 Ma apart</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_23</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_24</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_25</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_5</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_26</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_6</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_27</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_7</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_28</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_8</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_zhang_2020_29</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The calculation of d13C_CO2aq  follows Zhang et al. (2013)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_zhang_2020_50</t>
+    <t xml:space="preserve">phytoplankton_Zhang_2019_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60-63.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liu et al., 2009; updated here.; Updated to GTS2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5-67.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46-49.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55-58.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50-54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See table S4 (Pagani et al. (2011)  for list of age-depth constraints.; Updated to GTS2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">published TEX86 temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52-56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50-53.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51-54.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48-51.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54-58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98-104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_111</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1876,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1645,12 +1942,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1764,7 +2055,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1863,7 +2154,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2589,7 +2879,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2607,8 +2897,8 @@
       <c r="H5" t="n">
         <v>0.03712489</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2626,7 +2916,7 @@
         <v>-24.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04</v>
+        <v>0.0282842712474619</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2638,7 +2928,7 @@
         <v>24.6336722027576</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4257639177681</v>
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2655,11 +2945,11 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA5" t="s">
         <v>278</v>
@@ -2677,29 +2967,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77559534179805</v>
+        <v>1.76599281261216</v>
       </c>
       <c r="AG5" t="s">
         <v>279</v>
       </c>
-      <c r="AH5" t="e">
-        <v>#N/A</v>
+      <c r="AH5" t="s">
+        <v>280</v>
       </c>
       <c r="AI5" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2717,8 +3007,8 @@
       <c r="H6" t="n">
         <v>0.037591</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2736,7 +3026,7 @@
         <v>-24.69</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08</v>
+        <v>0.0565685424949238</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2748,7 +3038,7 @@
         <v>24.317326244402</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3629446749707</v>
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2765,11 +3055,11 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA6" t="s">
         <v>278</v>
@@ -2787,29 +3077,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83227262262168</v>
+        <v>1.82257462186765</v>
       </c>
       <c r="AG6" t="s">
         <v>279</v>
       </c>
-      <c r="AH6" t="e">
-        <v>#N/A</v>
+      <c r="AH6" t="s">
+        <v>283</v>
       </c>
       <c r="AI6" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2827,8 +3117,8 @@
       <c r="H7" t="n">
         <v>0.09965047</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2846,7 +3136,7 @@
         <v>-24.8061967689132</v>
       </c>
       <c r="O7" t="n">
-        <v>0.30233014638419</v>
+        <v>0.213779696665382</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2858,7 +3148,7 @@
         <v>26.8233929125304</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4731948463846</v>
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2875,11 +3165,11 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA7" t="s">
         <v>278</v>
@@ -2897,29 +3187,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.46529919926486</v>
+        <v>1.45621935675142</v>
       </c>
       <c r="AG7" t="s">
         <v>279</v>
       </c>
-      <c r="AH7" t="e">
-        <v>#N/A</v>
+      <c r="AH7" t="s">
+        <v>285</v>
       </c>
       <c r="AI7" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2937,8 +3227,8 @@
       <c r="H8" t="n">
         <v>0.10005369</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2956,7 +3246,7 @@
         <v>-25.1762340058953</v>
       </c>
       <c r="O8" t="n">
-        <v>0.554775231452652</v>
+        <v>0.392285328194507</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2968,7 +3258,7 @@
         <v>26.8726395457918</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4806621250915</v>
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -2985,11 +3275,11 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA8" t="s">
         <v>278</v>
@@ -3007,29 +3297,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62286900553277</v>
+        <v>1.61352374032653</v>
       </c>
       <c r="AG8" t="s">
         <v>279</v>
       </c>
-      <c r="AH8" t="e">
-        <v>#N/A</v>
+      <c r="AH8" t="s">
+        <v>287</v>
       </c>
       <c r="AI8" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3047,8 +3337,8 @@
       <c r="H9" t="n">
         <v>0.10045691</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3066,7 +3356,7 @@
         <v>-25.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0.78</v>
+        <v>0.551543289325507</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3078,7 +3368,7 @@
         <v>26.9250121315814</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5184818751849</v>
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3095,11 +3385,11 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA9" t="s">
         <v>278</v>
@@ -3117,29 +3407,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62522430950365</v>
+        <v>1.61587507684236</v>
       </c>
       <c r="AG9" t="s">
         <v>279</v>
       </c>
-      <c r="AH9" t="e">
-        <v>#N/A</v>
+      <c r="AH9" t="s">
+        <v>289</v>
       </c>
       <c r="AI9" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3157,8 +3447,8 @@
       <c r="H10" t="n">
         <v>0.12477635</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3176,7 +3466,7 @@
         <v>-24.51</v>
       </c>
       <c r="O10" t="n">
-        <v>0.58</v>
+        <v>0.410121933088197</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3188,7 +3478,7 @@
         <v>29.8947813003059</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5421410915139</v>
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3205,11 +3495,11 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA10" t="s">
         <v>278</v>
@@ -3227,29 +3517,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69622858902572</v>
+        <v>1.68675975129848</v>
       </c>
       <c r="AG10" t="s">
         <v>279</v>
       </c>
-      <c r="AH10" t="e">
-        <v>#N/A</v>
+      <c r="AH10" t="s">
+        <v>291</v>
       </c>
       <c r="AI10" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3267,8 +3557,8 @@
       <c r="H11" t="n">
         <v>0.13750922</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3286,7 +3576,7 @@
         <v>-24.98</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1</v>
+        <v>0.0707106781186548</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3298,7 +3588,7 @@
         <v>26.0067065559531</v>
       </c>
       <c r="S11" t="n">
-        <v>4.0421941213526</v>
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3315,11 +3605,11 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA11" t="s">
         <v>278</v>
@@ -3337,29 +3627,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.69593072595765</v>
+        <v>1.68646238997386</v>
       </c>
       <c r="AG11" t="s">
         <v>279</v>
       </c>
-      <c r="AH11" t="e">
-        <v>#N/A</v>
+      <c r="AH11" t="s">
+        <v>293</v>
       </c>
       <c r="AI11" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3377,8 +3667,8 @@
       <c r="H12" t="n">
         <v>0.15730934</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3396,7 +3686,7 @@
         <v>-23.3665787928722</v>
       </c>
       <c r="O12" t="n">
-        <v>0.140480061314442</v>
+        <v>0.0993344039769437</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3408,7 +3698,7 @@
         <v>24.8571625302204</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5302557980721</v>
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3425,11 +3715,11 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA12" t="s">
         <v>278</v>
@@ -3447,29 +3737,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83530983746914</v>
+        <v>1.82560672059697</v>
       </c>
       <c r="AG12" t="s">
         <v>279</v>
       </c>
-      <c r="AH12" t="e">
-        <v>#N/A</v>
+      <c r="AH12" t="s">
+        <v>295</v>
       </c>
       <c r="AI12" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3487,8 +3777,8 @@
       <c r="H13" t="n">
         <v>0.15994936</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3506,7 +3796,7 @@
         <v>-23.8111118929164</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32903970623076</v>
+        <v>0.939772988741944</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3518,7 +3808,7 @@
         <v>26.1404428643064</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1927760331553</v>
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3535,11 +3825,11 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA13" t="s">
         <v>278</v>
@@ -3557,29 +3847,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.70921995216</v>
+        <v>1.69972923078216</v>
       </c>
       <c r="AG13" t="s">
         <v>279</v>
       </c>
-      <c r="AH13" t="e">
-        <v>#N/A</v>
+      <c r="AH13" t="s">
+        <v>297</v>
       </c>
       <c r="AI13" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3597,8 +3887,8 @@
       <c r="H14" t="n">
         <v>0.18238949</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3616,7 +3906,7 @@
         <v>-24.75</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3628,7 +3918,7 @@
         <v>27.5641874716509</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8091267152406</v>
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3645,11 +3935,11 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA14" t="s">
         <v>278</v>
@@ -3667,29 +3957,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75348894236323</v>
+        <v>1.74392365089569</v>
       </c>
       <c r="AG14" t="s">
         <v>279</v>
       </c>
-      <c r="AH14" t="e">
-        <v>#N/A</v>
+      <c r="AH14" t="s">
+        <v>299</v>
       </c>
       <c r="AI14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3707,8 +3997,8 @@
       <c r="H15" t="n">
         <v>0.1837095</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3726,7 +4016,7 @@
         <v>-25.45</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06</v>
+        <v>0.0424264068711928</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3738,7 +4028,7 @@
         <v>26.6496698011663</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4395386094074</v>
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3755,11 +4045,11 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA15" t="s">
         <v>278</v>
@@ -3777,29 +4067,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53034798914235</v>
+        <v>1.52115857344747</v>
       </c>
       <c r="AG15" t="s">
         <v>279</v>
       </c>
-      <c r="AH15" t="e">
-        <v>#N/A</v>
+      <c r="AH15" t="s">
+        <v>301</v>
       </c>
       <c r="AI15" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3817,8 +4107,8 @@
       <c r="H16" t="n">
         <v>0.21670969</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3836,7 +4126,7 @@
         <v>-25.93</v>
       </c>
       <c r="O16" t="n">
-        <v>0.38</v>
+        <v>0.268700576850888</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3848,7 +4138,7 @@
         <v>27.7851282520203</v>
       </c>
       <c r="S16" t="n">
-        <v>4.896221581473</v>
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3865,11 +4155,11 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA16" t="s">
         <v>278</v>
@@ -3887,29 +4177,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.52539278716753</v>
+        <v>1.51621171839571</v>
       </c>
       <c r="AG16" t="s">
         <v>279</v>
       </c>
-      <c r="AH16" t="e">
-        <v>#N/A</v>
+      <c r="AH16" t="s">
+        <v>303</v>
       </c>
       <c r="AI16" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3927,8 +4217,8 @@
       <c r="H17" t="n">
         <v>0.2180297</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3946,7 +4236,7 @@
         <v>-25.33</v>
       </c>
       <c r="O17" t="n">
-        <v>0.24</v>
+        <v>0.169705627484771</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3958,7 +4248,7 @@
         <v>27.3040182707569</v>
       </c>
       <c r="S17" t="n">
-        <v>4.6959132273838</v>
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -3975,11 +4265,11 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA17" t="s">
         <v>278</v>
@@ -3997,29 +4287,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.38122316369297</v>
+        <v>1.37228494531609</v>
       </c>
       <c r="AG17" t="s">
         <v>279</v>
       </c>
-      <c r="AH17" t="e">
-        <v>#N/A</v>
+      <c r="AH17" t="s">
+        <v>305</v>
       </c>
       <c r="AI17" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4037,8 +4327,8 @@
       <c r="H18" t="n">
         <v>0.24100451</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4056,7 +4346,7 @@
         <v>-24.44</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>0.834386001800126</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4068,7 +4358,7 @@
         <v>26.7811881564485</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4641703064084</v>
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4085,11 +4375,11 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#N/A</v>
+      <c r="Y18" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA18" t="s">
         <v>278</v>
@@ -4107,29 +4397,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.58922613976532</v>
+        <v>1.57993754518804</v>
       </c>
       <c r="AG18" t="s">
         <v>279</v>
       </c>
-      <c r="AH18" t="e">
-        <v>#N/A</v>
+      <c r="AH18" t="s">
+        <v>307</v>
       </c>
       <c r="AI18" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4147,8 +4437,8 @@
       <c r="H19" t="n">
         <v>0.24388653</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4166,7 +4456,7 @@
         <v>-24.67</v>
       </c>
       <c r="O19" t="n">
-        <v>0.42</v>
+        <v>0.29698484809835</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4178,7 +4468,7 @@
         <v>27.4819586498228</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7872883242637</v>
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4195,11 +4485,11 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#N/A</v>
+      <c r="Y19" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA19" t="s">
         <v>278</v>
@@ -4217,29 +4507,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53756005777549</v>
+        <v>1.52835849351786</v>
       </c>
       <c r="AG19" t="s">
         <v>279</v>
       </c>
-      <c r="AH19" t="e">
-        <v>#N/A</v>
+      <c r="AH19" t="s">
+        <v>309</v>
       </c>
       <c r="AI19" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4257,8 +4547,8 @@
       <c r="H20" t="n">
         <v>0.25321004</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4276,7 +4566,7 @@
         <v>-24.98</v>
       </c>
       <c r="O20" t="n">
-        <v>0.52</v>
+        <v>0.367695526217005</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4288,7 +4578,7 @@
         <v>24.8286570921282</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5129253865843</v>
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4305,11 +4595,11 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#N/A</v>
+      <c r="Y20" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA20" t="s">
         <v>278</v>
@@ -4327,29 +4617,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.59879639477958</v>
+        <v>1.58949167932916</v>
       </c>
       <c r="AG20" t="s">
         <v>279</v>
       </c>
-      <c r="AH20" t="e">
-        <v>#N/A</v>
+      <c r="AH20" t="s">
+        <v>311</v>
       </c>
       <c r="AI20" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4367,8 +4657,8 @@
       <c r="H21" t="n">
         <v>0.25452784</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4386,7 +4676,7 @@
         <v>-25.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7</v>
+        <v>0.494974746830583</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4398,7 +4688,7 @@
         <v>24.6002063302755</v>
       </c>
       <c r="S21" t="n">
-        <v>3.427139000128</v>
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4415,11 +4705,11 @@
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#N/A</v>
+      <c r="Y21" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA21" t="s">
         <v>278</v>
@@ -4437,29 +4727,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.68679188739485</v>
+        <v>1.67733894557316</v>
       </c>
       <c r="AG21" t="s">
         <v>279</v>
       </c>
-      <c r="AH21" t="e">
-        <v>#N/A</v>
+      <c r="AH21" t="s">
+        <v>313</v>
       </c>
       <c r="AI21" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4477,8 +4767,8 @@
       <c r="H22" t="n">
         <v>0.26902366</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4496,7 +4786,7 @@
         <v>-25.06</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3</v>
+        <v>0.212132034355964</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4508,7 +4798,7 @@
         <v>24.7148437797699</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4975351904814</v>
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4525,11 +4815,11 @@
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#N/A</v>
+      <c r="Y22" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA22" t="s">
         <v>278</v>
@@ -4547,29 +4837,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.66766090207034</v>
+        <v>1.65824018595078</v>
       </c>
       <c r="AG22" t="s">
         <v>279</v>
       </c>
-      <c r="AH22" t="e">
-        <v>#N/A</v>
+      <c r="AH22" t="s">
+        <v>315</v>
       </c>
       <c r="AI22" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4587,8 +4877,8 @@
       <c r="H23" t="n">
         <v>0.29274409</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4606,7 +4896,7 @@
         <v>-24.07</v>
       </c>
       <c r="O23" t="n">
-        <v>0.08</v>
+        <v>0.0565685424949238</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4618,7 +4908,7 @@
         <v>28.0321765570932</v>
       </c>
       <c r="S23" t="n">
-        <v>4.9827926373886</v>
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4635,11 +4925,11 @@
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#N/A</v>
+      <c r="Y23" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA23" t="s">
         <v>278</v>
@@ -4657,29 +4947,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57443613706509</v>
+        <v>1.56517245590514</v>
       </c>
       <c r="AG23" t="s">
         <v>279</v>
       </c>
-      <c r="AH23" t="e">
-        <v>#N/A</v>
+      <c r="AH23" t="s">
+        <v>317</v>
       </c>
       <c r="AI23" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4697,8 +4987,8 @@
       <c r="H24" t="n">
         <v>0.30855771</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4716,7 +5006,7 @@
         <v>-25.53</v>
       </c>
       <c r="O24" t="n">
-        <v>0.12</v>
+        <v>0.0848528137423857</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4728,7 +5018,7 @@
         <v>28.7835765060275</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1982478026947</v>
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4745,11 +5035,11 @@
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#N/A</v>
+      <c r="Y24" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA24" t="s">
         <v>278</v>
@@ -4767,29 +5057,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.58133773779801</v>
+        <v>1.57206243105131</v>
       </c>
       <c r="AG24" t="s">
         <v>279</v>
       </c>
-      <c r="AH24" t="e">
-        <v>#N/A</v>
+      <c r="AH24" t="s">
+        <v>319</v>
       </c>
       <c r="AI24" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4807,8 +5097,8 @@
       <c r="H25" t="n">
         <v>0.34330865</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4826,7 +5116,7 @@
         <v>-25.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04</v>
+        <v>0.0282842712474619</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4838,7 +5128,7 @@
         <v>26.150448201086</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1228870109895</v>
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4855,11 +5145,11 @@
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#N/A</v>
+      <c r="Y25" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.264</v>
       </c>
       <c r="AA25" t="s">
         <v>278</v>
@@ -4877,29 +5167,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63015961159006</v>
+        <v>1.6208020655266</v>
       </c>
       <c r="AG25" t="s">
         <v>279</v>
       </c>
-      <c r="AH25" t="e">
-        <v>#N/A</v>
+      <c r="AH25" t="s">
+        <v>321</v>
       </c>
       <c r="AI25" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4917,8 +5207,8 @@
       <c r="H26" t="n">
         <v>0.02999447</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4936,7 +5226,7 @@
         <v>-23.543</v>
       </c>
       <c r="O26" t="n">
-        <v>0.118000000000002</v>
+        <v>0.0834386001800141</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4948,7 +5238,7 @@
         <v>28.13</v>
       </c>
       <c r="S26" t="n">
-        <v>5.0127986982738</v>
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -4965,11 +5255,11 @@
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#N/A</v>
+      <c r="Y26" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA26" t="s">
         <v>278</v>
@@ -4987,29 +5277,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8083475862069</v>
+        <v>1.79868988662313</v>
       </c>
       <c r="AG26" t="s">
         <v>279</v>
       </c>
-      <c r="AH26" t="e">
-        <v>#N/A</v>
+      <c r="AH26" t="s">
+        <v>323</v>
       </c>
       <c r="AI26" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ26" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5027,8 +5317,8 @@
       <c r="H27" t="n">
         <v>0.03954827</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5046,7 +5336,7 @@
         <v>-24.05</v>
       </c>
       <c r="O27" t="n">
-        <v>0.414000000000001</v>
+        <v>0.292742207411232</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5058,7 +5348,7 @@
         <v>28.51</v>
       </c>
       <c r="S27" t="n">
-        <v>5.0923719437042</v>
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5075,11 +5365,11 @@
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#N/A</v>
+      <c r="Y27" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA27" t="s">
         <v>278</v>
@@ -5097,29 +5387,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.61246034482759</v>
+        <v>1.60313261276947</v>
       </c>
       <c r="AG27" t="s">
         <v>279</v>
       </c>
-      <c r="AH27" t="e">
-        <v>#N/A</v>
+      <c r="AH27" t="s">
+        <v>326</v>
       </c>
       <c r="AI27" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ27" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5137,8 +5427,8 @@
       <c r="H28" t="n">
         <v>0.04910211</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5156,7 +5446,7 @@
         <v>-23.8055</v>
       </c>
       <c r="O28" t="n">
-        <v>0.149999999999999</v>
+        <v>0.106066017177981</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5168,7 +5458,7 @@
         <v>27.23</v>
       </c>
       <c r="S28" t="n">
-        <v>4.7071659442802</v>
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5185,11 +5475,11 @@
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#N/A</v>
+      <c r="Y28" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA28" t="s">
         <v>278</v>
@@ -5207,29 +5497,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.71652142857143</v>
+        <v>1.70701840802552</v>
       </c>
       <c r="AG28" t="s">
         <v>279</v>
       </c>
-      <c r="AH28" t="e">
-        <v>#N/A</v>
+      <c r="AH28" t="s">
+        <v>328</v>
       </c>
       <c r="AI28" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ28" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5247,8 +5537,8 @@
       <c r="H29" t="n">
         <v>0.06147872</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5266,7 +5556,7 @@
         <v>-23.969</v>
       </c>
       <c r="O29" t="n">
-        <v>0.488</v>
+        <v>0.345068109219035</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5278,7 +5568,7 @@
         <v>28.07</v>
       </c>
       <c r="S29" t="n">
-        <v>4.9693709738384</v>
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5295,11 +5585,11 @@
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#N/A</v>
+      <c r="Y29" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA29" t="s">
         <v>278</v>
@@ -5317,29 +5607,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.66189758454106</v>
+        <v>1.65248657659653</v>
       </c>
       <c r="AG29" t="s">
         <v>279</v>
       </c>
-      <c r="AH29" t="e">
-        <v>#N/A</v>
+      <c r="AH29" t="s">
+        <v>330</v>
       </c>
       <c r="AI29" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ29" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5357,8 +5647,8 @@
       <c r="H30" t="n">
         <v>0.0746889</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5376,7 +5666,7 @@
         <v>-24.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0.224000000000004</v>
+        <v>0.158391918985789</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5388,7 +5678,7 @@
         <v>28.95</v>
       </c>
       <c r="S30" t="n">
-        <v>5.2694257155472</v>
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5405,11 +5695,11 @@
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#N/A</v>
+      <c r="Y30" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA30" t="s">
         <v>278</v>
@@ -5427,29 +5717,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.53605806451613</v>
+        <v>1.52685903033139</v>
       </c>
       <c r="AG30" t="s">
         <v>279</v>
       </c>
-      <c r="AH30" t="e">
-        <v>#N/A</v>
+      <c r="AH30" t="s">
+        <v>332</v>
       </c>
       <c r="AI30" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ30" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5467,8 +5757,8 @@
       <c r="H31" t="n">
         <v>0.08938702</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5486,7 +5776,7 @@
         <v>-24.2365</v>
       </c>
       <c r="O31" t="n">
-        <v>0.405999999999999</v>
+        <v>0.287085353161737</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5498,7 +5788,7 @@
         <v>29.07</v>
       </c>
       <c r="S31" t="n">
-        <v>5.2448007776083</v>
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5515,11 +5805,11 @@
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#N/A</v>
+      <c r="Y31" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA31" t="s">
         <v>278</v>
@@ -5537,29 +5827,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.41719015384615</v>
+        <v>1.40819134990657</v>
       </c>
       <c r="AG31" t="s">
         <v>279</v>
       </c>
-      <c r="AH31" t="e">
-        <v>#N/A</v>
+      <c r="AH31" t="s">
+        <v>334</v>
       </c>
       <c r="AI31" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ31" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5577,8 +5867,8 @@
       <c r="H32" t="n">
         <v>0.1013744</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5596,7 +5886,7 @@
         <v>-23.994</v>
       </c>
       <c r="O32" t="n">
-        <v>0.100000000000001</v>
+        <v>0.0707106781186558</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5608,7 +5898,7 @@
         <v>29.18</v>
       </c>
       <c r="S32" t="n">
-        <v>5.3042931033176</v>
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5625,11 +5915,11 @@
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#N/A</v>
+      <c r="Y32" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA32" t="s">
         <v>278</v>
@@ -5647,29 +5937,29 @@
         <v>#N/A</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.49843087248322</v>
+        <v>1.48929522043284</v>
       </c>
       <c r="AG32" t="s">
         <v>279</v>
       </c>
-      <c r="AH32" t="e">
-        <v>#N/A</v>
+      <c r="AH32" t="s">
+        <v>336</v>
       </c>
       <c r="AI32" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ32" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5687,8 +5977,8 @@
       <c r="H33" t="n">
         <v>0.1432684</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5706,7 +5996,7 @@
         <v>-24.3855</v>
       </c>
       <c r="O33" t="n">
-        <v>0.324000000000005</v>
+        <v>0.229102597104445</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5718,7 +6008,7 @@
         <v>29</v>
       </c>
       <c r="S33" t="n">
-        <v>5.2808541587794</v>
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5735,11 +6025,11 @@
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#N/A</v>
+      <c r="Y33" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.168</v>
       </c>
       <c r="AA33" t="s">
         <v>278</v>
@@ -5757,112 +6047,2550 @@
         <v>#N/A</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.58922985074627</v>
+        <v>1.57994124991792</v>
       </c>
       <c r="AG33" t="s">
         <v>279</v>
       </c>
-      <c r="AH33" t="e">
-        <v>#N/A</v>
+      <c r="AH33" t="s">
+        <v>338</v>
       </c>
       <c r="AI33" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ33" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="R34" s="11"/>
-      <c r="V34" s="11"/>
+      <c r="A34" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" t="s">
+        <v>271</v>
+      </c>
+      <c r="C34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D34" t="s">
+        <v>273</v>
+      </c>
+      <c r="E34" t="s">
+        <v>274</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>32.7322731018066</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.160577822251197</v>
+      </c>
+      <c r="J34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L34" t="s">
+        <v>340</v>
+      </c>
+      <c r="M34" t="s">
+        <v>276</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-34.80425</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>9.43964655565767</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V34" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>7.15786403940886</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>6.11982479977577</v>
+      </c>
+      <c r="AD34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.41707175110578</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>341</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>342</v>
+      </c>
+      <c r="AJ34" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="R35" s="11"/>
-      <c r="V35" s="11"/>
+      <c r="A35" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" t="s">
+        <v>271</v>
+      </c>
+      <c r="C35" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35" t="s">
+        <v>273</v>
+      </c>
+      <c r="E35" t="s">
+        <v>274</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>33.309211730957</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.161971295590638</v>
+      </c>
+      <c r="J35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L35" t="s">
+        <v>340</v>
+      </c>
+      <c r="M35" t="s">
+        <v>276</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-34.70525</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R35" s="11" t="n">
+        <v>12.2446132582512</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V35" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>6.84508706467662</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>5.66043888419682</v>
+      </c>
+      <c r="AD35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.27968170307742</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>344</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>345</v>
+      </c>
+      <c r="AJ35" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="R36" s="11"/>
-      <c r="V36" s="11"/>
+      <c r="A36" t="s">
+        <v>346</v>
+      </c>
+      <c r="B36" t="s">
+        <v>271</v>
+      </c>
+      <c r="C36" t="s">
+        <v>272</v>
+      </c>
+      <c r="D36" t="s">
+        <v>273</v>
+      </c>
+      <c r="E36" t="s">
+        <v>274</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>33.5326957702637</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.162598564183473</v>
+      </c>
+      <c r="J36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L36" t="s">
+        <v>340</v>
+      </c>
+      <c r="M36" t="s">
+        <v>276</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-34.05025</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R36" s="11" t="n">
+        <v>9.98416574935819</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V36" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>7.32369705882353</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.33681538786374</v>
+      </c>
+      <c r="AD36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.48991536921921</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>347</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ36" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="R37" s="11"/>
-      <c r="V37" s="11"/>
+      <c r="A37" t="s">
+        <v>349</v>
+      </c>
+      <c r="B37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C37" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" t="s">
+        <v>273</v>
+      </c>
+      <c r="E37" t="s">
+        <v>274</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36.3888053894043</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.170610480799422</v>
+      </c>
+      <c r="J37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L37" t="s">
+        <v>340</v>
+      </c>
+      <c r="M37" t="s">
+        <v>276</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-33.997</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R37" s="11" t="n">
+        <v>21.7334984863641</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V37" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.41997669902912</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.94182995229779</v>
+      </c>
+      <c r="AD37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.09294822116539</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>351</v>
+      </c>
+      <c r="AJ37" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="R38" s="11"/>
-      <c r="V38" s="11"/>
+      <c r="A38" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" t="s">
+        <v>271</v>
+      </c>
+      <c r="C38" t="s">
+        <v>272</v>
+      </c>
+      <c r="D38" t="s">
+        <v>273</v>
+      </c>
+      <c r="E38" t="s">
+        <v>274</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37.0602684020996</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.179234822876983</v>
+      </c>
+      <c r="J38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L38" t="s">
+        <v>340</v>
+      </c>
+      <c r="M38" t="s">
+        <v>276</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-33.65725</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R38" s="11" t="n">
+        <v>20.1203832343391</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V38" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8.30478994974875</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.52368325213002</v>
+      </c>
+      <c r="AD38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.92086908478567</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>353</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>354</v>
+      </c>
+      <c r="AJ38" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="R39" s="11"/>
-      <c r="V39" s="11"/>
+      <c r="A39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" t="s">
+        <v>271</v>
+      </c>
+      <c r="C39" t="s">
+        <v>272</v>
+      </c>
+      <c r="D39" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" t="s">
+        <v>274</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>32.5897445678711</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.158956265422346</v>
+      </c>
+      <c r="J39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L39" t="s">
+        <v>356</v>
+      </c>
+      <c r="M39" t="s">
+        <v>276</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-30.0755</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>29.7833038995423</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V39" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>6.1146595</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.67782377985921</v>
+      </c>
+      <c r="AD39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.95883494548579</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>358</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>359</v>
+      </c>
+      <c r="AJ39" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="R40" s="11"/>
-      <c r="V40" s="11"/>
+      <c r="A40" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" t="s">
+        <v>271</v>
+      </c>
+      <c r="C40" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" t="s">
+        <v>273</v>
+      </c>
+      <c r="E40" t="s">
+        <v>274</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>33.0903625488281</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.160959808439161</v>
+      </c>
+      <c r="J40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L40" t="s">
+        <v>356</v>
+      </c>
+      <c r="M40" t="s">
+        <v>276</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-28.88425</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R40" s="11" t="n">
+        <v>26.3393995013186</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V40" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.2157245</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.79965588571006</v>
+      </c>
+      <c r="AD40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.56396980897726</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>361</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>362</v>
+      </c>
+      <c r="AJ40" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="R41" s="11"/>
-      <c r="V41" s="11"/>
+      <c r="A41" t="s">
+        <v>363</v>
+      </c>
+      <c r="B41" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" t="s">
+        <v>273</v>
+      </c>
+      <c r="E41" t="s">
+        <v>274</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>33.381664276123</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.162769495184743</v>
+      </c>
+      <c r="J41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L41" t="s">
+        <v>356</v>
+      </c>
+      <c r="M41" t="s">
+        <v>276</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-29.74525</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>28.0636062848367</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V41" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>5.520035</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.81254325061032</v>
+      </c>
+      <c r="AD41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.69764088321898</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>364</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>365</v>
+      </c>
+      <c r="AJ41" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
-      <c r="R42" s="11"/>
-      <c r="V42" s="11"/>
+      <c r="A42" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" t="s">
+        <v>271</v>
+      </c>
+      <c r="C42" t="s">
+        <v>272</v>
+      </c>
+      <c r="D42" t="s">
+        <v>273</v>
+      </c>
+      <c r="E42" t="s">
+        <v>274</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>34.0679092407227</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.164939990026726</v>
+      </c>
+      <c r="J42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L42" t="s">
+        <v>356</v>
+      </c>
+      <c r="M42" t="s">
+        <v>276</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-30.9115</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R42" s="11" t="n">
+        <v>28.0843947313704</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V42" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>6.3741845</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>5.89525003392148</v>
+      </c>
+      <c r="AD42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.07283359338845</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>367</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>368</v>
+      </c>
+      <c r="AJ42" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="43" ht="19" customHeight="1">
-      <c r="R43" s="11"/>
-      <c r="V43" s="11"/>
+      <c r="A43" t="s">
+        <v>363</v>
+      </c>
+      <c r="B43" t="s">
+        <v>271</v>
+      </c>
+      <c r="C43" t="s">
+        <v>272</v>
+      </c>
+      <c r="D43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E43" t="s">
+        <v>274</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>34.613109588623</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.168696459535655</v>
+      </c>
+      <c r="J43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L43" t="s">
+        <v>356</v>
+      </c>
+      <c r="M43" t="s">
+        <v>276</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-31.5175</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R43" s="11" t="n">
+        <v>34.2697531776774</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V43" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.94467512437811</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5.00855267971821</v>
+      </c>
+      <c r="AD43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.88416780750112</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>369</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ43" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="44" ht="19" customHeight="1">
-      <c r="R44" s="11"/>
-      <c r="V44" s="11"/>
+      <c r="A44" t="s">
+        <v>371</v>
+      </c>
+      <c r="B44" t="s">
+        <v>271</v>
+      </c>
+      <c r="C44" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" t="s">
+        <v>273</v>
+      </c>
+      <c r="E44" t="s">
+        <v>274</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H44" t="n">
+        <v>35.116024017334</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.171504856496813</v>
+      </c>
+      <c r="J44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L44" t="s">
+        <v>356</v>
+      </c>
+      <c r="M44" t="s">
+        <v>276</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-31.26975</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R44" s="11" t="n">
+        <v>35.0654014917404</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V44" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>6.361384</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>6.34914904117958</v>
+      </c>
+      <c r="AD44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3.06721086073272</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>372</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>373</v>
+      </c>
+      <c r="AJ44" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="45" ht="19" customHeight="1">
-      <c r="R45" s="11"/>
-      <c r="V45" s="11"/>
+      <c r="A45" t="s">
+        <v>360</v>
+      </c>
+      <c r="B45" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E45" t="s">
+        <v>274</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>30.6120376586914</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.149292886313145</v>
+      </c>
+      <c r="J45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L45" t="s">
+        <v>356</v>
+      </c>
+      <c r="M45" t="s">
+        <v>276</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-30.4305</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R45" s="11" t="n">
+        <v>34.616944192036</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V45" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>4.82223861386138</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.73884547415873</v>
+      </c>
+      <c r="AD45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.39112765893938</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>374</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>375</v>
+      </c>
+      <c r="AJ45" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="R46" s="11"/>
-      <c r="V46" s="11"/>
+      <c r="A46" t="s">
+        <v>376</v>
+      </c>
+      <c r="B46" t="s">
+        <v>271</v>
+      </c>
+      <c r="C46" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" t="s">
+        <v>273</v>
+      </c>
+      <c r="E46" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>32.4226531982422</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.157581411247463</v>
+      </c>
+      <c r="J46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L46" t="s">
+        <v>356</v>
+      </c>
+      <c r="M46" t="s">
+        <v>276</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-29.45975</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R46" s="11" t="n">
+        <v>35.4461352262789</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V46" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>5.12184848484848</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.23813832268537</v>
+      </c>
+      <c r="AD46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.52273394037978</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>378</v>
+      </c>
+      <c r="AJ46" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="47" ht="19" customHeight="1">
-      <c r="R47" s="11"/>
-      <c r="V47" s="11"/>
+      <c r="A47" t="s">
+        <v>379</v>
+      </c>
+      <c r="B47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" t="s">
+        <v>273</v>
+      </c>
+      <c r="E47" t="s">
+        <v>274</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H47" t="n">
+        <v>32.5073776245117</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.157971396447939</v>
+      </c>
+      <c r="J47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L47" t="s">
+        <v>356</v>
+      </c>
+      <c r="M47" t="s">
+        <v>276</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-29.244</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>35.6265119485304</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V47" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>4.7257335</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.71097791788634</v>
+      </c>
+      <c r="AD47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.34873693551817</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>380</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>381</v>
+      </c>
+      <c r="AJ47" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="48" ht="19" customHeight="1">
-      <c r="R48" s="11"/>
-      <c r="V48" s="11"/>
+      <c r="A48" t="s">
+        <v>382</v>
+      </c>
+      <c r="B48" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" t="s">
+        <v>272</v>
+      </c>
+      <c r="D48" t="s">
+        <v>273</v>
+      </c>
+      <c r="E48" t="s">
+        <v>274</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>33.210578918457</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.161292564066025</v>
+      </c>
+      <c r="J48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L48" t="s">
+        <v>356</v>
+      </c>
+      <c r="M48" t="s">
+        <v>276</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-29.59825</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R48" s="11" t="n">
+        <v>34.9429535009919</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V48" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>5.227997</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.38482674309452</v>
+      </c>
+      <c r="AD48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.56936061297065</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>383</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>384</v>
+      </c>
+      <c r="AJ48" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="R49" s="11"/>
-      <c r="V49" s="11"/>
+      <c r="A49" t="s">
+        <v>385</v>
+      </c>
+      <c r="B49" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" t="s">
+        <v>272</v>
+      </c>
+      <c r="D49" t="s">
+        <v>273</v>
+      </c>
+      <c r="E49" t="s">
+        <v>274</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H49" t="n">
+        <v>33.5992813110352</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.163309283963162</v>
+      </c>
+      <c r="J49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L49" t="s">
+        <v>356</v>
+      </c>
+      <c r="M49" t="s">
+        <v>276</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-30.676</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R49" s="11" t="n">
+        <v>27.9261912479</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V49" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>5.8842305</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.44563506075772</v>
+      </c>
+      <c r="AD49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.85761697250607</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>386</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>387</v>
+      </c>
+      <c r="AJ49" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="50" ht="19" customHeight="1">
-      <c r="R50" s="11"/>
-      <c r="V50" s="11"/>
+      <c r="A50" t="s">
+        <v>388</v>
+      </c>
+      <c r="B50" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" t="s">
+        <v>273</v>
+      </c>
+      <c r="E50" t="s">
+        <v>274</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>33.9171524047852</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.165009389957635</v>
+      </c>
+      <c r="J50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L50" t="s">
+        <v>356</v>
+      </c>
+      <c r="M50" t="s">
+        <v>276</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-31.327</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R50" s="11" t="n">
+        <v>34.830106374696</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V50" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>6.10986649999999</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.86033600125927</v>
+      </c>
+      <c r="AD50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.95672957791273</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>389</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>390</v>
+      </c>
+      <c r="AJ50" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="51" ht="19" customHeight="1">
-      <c r="R51" s="11"/>
-      <c r="V51" s="11"/>
+      <c r="A51" t="s">
+        <v>391</v>
+      </c>
+      <c r="B51" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" t="s">
+        <v>272</v>
+      </c>
+      <c r="D51" t="s">
+        <v>273</v>
+      </c>
+      <c r="E51" t="s">
+        <v>274</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H51" t="n">
+        <v>35.0923728942871</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.171005589157166</v>
+      </c>
+      <c r="J51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L51" t="s">
+        <v>356</v>
+      </c>
+      <c r="M51" t="s">
+        <v>276</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-30.83675</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R51" s="11" t="n">
+        <v>34.2053980370755</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V51" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>6.757402</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>5.59118042825399</v>
+      </c>
+      <c r="AD51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>3.24116526414324</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>392</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>393</v>
+      </c>
+      <c r="AJ51" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="52" ht="19" customHeight="1">
-      <c r="R52" s="11"/>
-      <c r="V52" s="11"/>
+      <c r="A52" t="s">
+        <v>394</v>
+      </c>
+      <c r="B52" t="s">
+        <v>271</v>
+      </c>
+      <c r="C52" t="s">
+        <v>272</v>
+      </c>
+      <c r="D52" t="s">
+        <v>273</v>
+      </c>
+      <c r="E52" t="s">
+        <v>274</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>35.5222396850586</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.173006117486608</v>
+      </c>
+      <c r="J52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L52" t="s">
+        <v>356</v>
+      </c>
+      <c r="M52" t="s">
+        <v>276</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-33.27375</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R52" s="11" t="n">
+        <v>33.4814800725394</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V52" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>6.596491</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.59838628020592</v>
+      </c>
+      <c r="AD52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3.17048368652003</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>395</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>396</v>
+      </c>
+      <c r="AJ52" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="53" ht="19" customHeight="1">
-      <c r="R53" s="11"/>
-      <c r="V53" s="11"/>
+      <c r="A53" t="s">
+        <v>397</v>
+      </c>
+      <c r="B53" t="s">
+        <v>271</v>
+      </c>
+      <c r="C53" t="s">
+        <v>272</v>
+      </c>
+      <c r="D53" t="s">
+        <v>273</v>
+      </c>
+      <c r="E53" t="s">
+        <v>274</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>35.8047637939453</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.174296621896064</v>
+      </c>
+      <c r="J53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L53" t="s">
+        <v>356</v>
+      </c>
+      <c r="M53" t="s">
+        <v>276</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-30.558</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R53" s="11" t="n">
+        <v>34.013686928431</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V53" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>6.67189</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>4.37605231436855</v>
+      </c>
+      <c r="AD53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.20360336305683</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>398</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ53" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="54" ht="19" customHeight="1">
-      <c r="R54" s="11"/>
-      <c r="V54" s="11"/>
+      <c r="A54" t="s">
+        <v>400</v>
+      </c>
+      <c r="B54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" t="s">
+        <v>272</v>
+      </c>
+      <c r="D54" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" t="s">
+        <v>274</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>33.371883392334</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.160964772717771</v>
+      </c>
+      <c r="J54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L54" t="s">
+        <v>356</v>
+      </c>
+      <c r="M54" t="s">
+        <v>276</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-33.55175</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R54" s="11" t="n">
+        <v>21.8146207584419</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V54" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>7.84384059405941</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>7.03312874674572</v>
+      </c>
+      <c r="AD54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.718393010033</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>401</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>402</v>
+      </c>
+      <c r="AJ54" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="55" ht="19" customHeight="1">
-      <c r="R55" s="11"/>
-      <c r="V55" s="11"/>
+      <c r="A55" t="s">
+        <v>403</v>
+      </c>
+      <c r="B55" t="s">
+        <v>271</v>
+      </c>
+      <c r="C55" t="s">
+        <v>272</v>
+      </c>
+      <c r="D55" t="s">
+        <v>273</v>
+      </c>
+      <c r="E55" t="s">
+        <v>274</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>33.7332611083984</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.164824195574707</v>
+      </c>
+      <c r="J55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L55" t="s">
+        <v>356</v>
+      </c>
+      <c r="M55" t="s">
+        <v>276</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-34.388</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R55" s="11" t="n">
+        <v>25.107643691821</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V55" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>8.7711423255814</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>6.31271447682253</v>
+      </c>
+      <c r="AD55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>4.12571848384593</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>404</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>405</v>
+      </c>
+      <c r="AJ55" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="56" ht="19" customHeight="1">
-      <c r="R56" s="11"/>
-      <c r="V56" s="11"/>
+      <c r="A56" t="s">
+        <v>406</v>
+      </c>
+      <c r="B56" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" t="s">
+        <v>272</v>
+      </c>
+      <c r="D56" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" t="s">
+        <v>274</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>35.9020309448242</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.172238312874359</v>
+      </c>
+      <c r="J56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L56" t="s">
+        <v>356</v>
+      </c>
+      <c r="M56" t="s">
+        <v>276</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-32.5585</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R56" s="11" t="n">
+        <v>25.0008041481619</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V56" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>8.64328217821782</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>5.27594185830883</v>
+      </c>
+      <c r="AD56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>4.06955478508827</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>407</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ56" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="R57" s="11"/>
@@ -6070,37 +8798,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
